--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136851697</v>
+        <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,25 +797,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -824,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745850</v>
+        <v>745865</v>
       </c>
       <c r="R3" t="n">
-        <v>7183533</v>
+        <v>7183540</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,49 +879,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136851697</t>
+          <t>https://artportalen.se/Sighting/136917793</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136851627</v>
+        <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,14 +930,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Janstorp , Vb</t>
+          <t>Janstorp, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745818</v>
+        <v>745850</v>
       </c>
       <c r="R4" t="n">
-        <v>7183515</v>
+        <v>7183533</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,16 +996,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136851627</t>
+          <t>https://artportalen.se/Sighting/136851697</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136851577</v>
+        <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,31 +1013,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,13 +1044,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745889</v>
+        <v>745837</v>
       </c>
       <c r="R5" t="n">
-        <v>7183489</v>
+        <v>7183524</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,35 +1082,1507 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136917995</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136918079</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83343</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>745889</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7183520</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918079</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136918085</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83343</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>745898</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7183533</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918085</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136918099</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92076</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>745891</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7183532</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918099</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136851627</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Janstorp , Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>745818</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7183515</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136851627</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136917754</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>745864</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7183575</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>rik förekomst på utspridda träd</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136917754</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136918021</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>745823</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7183518</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>rik förekomst på utspridda träd</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918021</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136918144</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>745882</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7183491</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>rik förekomst på utspridda träd</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918144</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136918034</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>745866</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7183510</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918034</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136851577</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>745889</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7183489</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136851577</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136917902</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>745850</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7183525</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136917902</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136918161</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>745882</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7183489</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918161</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136918199</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>745881</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7183446</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918199</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136917826</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Janstorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>745852</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7183528</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>7st överblommade</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136917826</t>
         </is>
       </c>
     </row>
@@ -1117,6 +2592,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -2471,7 +2471,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136918034</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136851577</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136917902</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136918161</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136918199</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136918034</v>
       </c>
       <c r="B13" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136851577</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>136917902</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136918161</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136918199</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -1924,11 +1924,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2039,11 +2035,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2154,11 +2146,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2269,11 +2257,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2384,11 +2368,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2502,11 +2482,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136918034</v>
       </c>
       <c r="B13" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136851577</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136917902</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136918161</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136918199</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136918034</v>
       </c>
       <c r="B13" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136851577</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136917902</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136918161</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136918199</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136918034</v>
       </c>
       <c r="B13" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136851577</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136917902</v>
       </c>
       <c r="B15" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136918161</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136918199</v>
       </c>
       <c r="B17" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136852009</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136851697</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136851627</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37134-2023 artfynd.xlsx
+++ b/artfynd/A 37134-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136917793</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136917995</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136918079</v>
       </c>
       <c r="B6" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136918085</v>
       </c>
       <c r="B7" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136918099</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136917754</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>136918021</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136918144</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136917826</v>
       </c>
       <c r="B18" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
